--- a/data/processed/harmonization/Nitrogen__Total_nitrogen/dois_filtering.xlsx
+++ b/data/processed/harmonization/Nitrogen__Total_nitrogen/dois_filtering.xlsx
@@ -1651,7 +1651,7 @@
         <v>109</v>
       </c>
       <c r="D31">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="E31" t="s">
         <v>184</v>
@@ -1671,7 +1671,7 @@
         <v>109</v>
       </c>
       <c r="D32">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E32" t="s">
         <v>185</v>
